--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486412_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486412_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7215</v>
+        <v>6.4105</v>
       </c>
       <c r="E2" t="n">
-        <v>8.210800000000001</v>
+        <v>8.838100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4893</v>
+        <v>-2.4276</v>
       </c>
       <c r="G2" t="n">
         <v>6.5935</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0895</v>
+        <v>-1.4006</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1644</v>
+        <v>-0.5371</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9251</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8826</v>
+        <v>1.76</v>
       </c>
       <c r="E3" t="n">
-        <v>1.143</v>
+        <v>2.4854</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7396</v>
+        <v>-0.7254</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2855</v>
+        <v>0.6868</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8699</v>
+        <v>0.4167</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1555</v>
+        <v>0.2701</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0469</v>
+        <v>3.0871</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9704</v>
+        <v>1.0981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765</v>
+        <v>1.989</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3324</v>
+        <v>-2.4003</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1004</v>
+        <v>-0.6814</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.232</v>
+        <v>-1.7188</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9936</v>
+        <v>-0.0796</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6187</v>
+        <v>-0.2319</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3749</v>
+        <v>0.1523</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7395</v>
+        <v>-0.3698</v>
       </c>
       <c r="W3" t="n">
+        <v>-0.3698</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3023</v>
+        <v>1.6946</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8419</v>
+        <v>1.3574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4605</v>
+        <v>0.3372</v>
       </c>
       <c r="G4" t="n">
         <v>0.674</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0688</v>
+        <v>-0.6766</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.399</v>
+        <v>0.1166</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6698</v>
+        <v>-0.7931</v>
       </c>
       <c r="V4" t="n">
         <v>0.1745</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1906</v>
+        <v>1.6803</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1934</v>
+        <v>0.249</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0028</v>
+        <v>1.4314</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6868</v>
+        <v>-0.2855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4167</v>
+        <v>0.8699</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2701</v>
+        <v>-1.1555</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0871</v>
+        <v>1.0469</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0981</v>
+        <v>0.9704</v>
       </c>
       <c r="L5" t="n">
-        <v>1.989</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4003</v>
+        <v>-1.3324</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6814</v>
+        <v>-0.1004</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7188</v>
+        <v>-1.232</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
+        <v>-1.5225</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9576</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7913</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.649</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.5239</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.1251</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.3698</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.3698</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4741</v>
+        <v>-0.2552</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3039</v>
+        <v>0.7077</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.778</v>
+        <v>-0.9629</v>
       </c>
       <c r="G6" t="n">
         <v>-1.082</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5857</v>
+        <v>0.8045</v>
       </c>
       <c r="T6" t="n">
-        <v>0.024</v>
+        <v>0.4278</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5617</v>
+        <v>0.3767</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1952</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0072</v>
+        <v>-0.9657</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4266</v>
+        <v>-0.6934</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5805</v>
+        <v>-0.2723</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3108</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9986</v>
+        <v>1.0401</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2402</v>
+        <v>0.9734</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2415</v>
+        <v>0.0667</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9875</v>
+        <v>-1.6493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4908</v>
+        <v>0.1933</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4783</v>
+        <v>-1.8426</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1062</v>
+        <v>-3.566</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4384</v>
+        <v>-1.2527</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-2.3133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0814</v>
+        <v>-0.1872</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2246</v>
+        <v>-0.5713</v>
       </c>
       <c r="L8" t="n">
-        <v>0.306</v>
+        <v>0.3841</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1876</v>
+        <v>-3.3788</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2138</v>
+        <v>-0.6814</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9738</v>
+        <v>-2.6974</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3926</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.579</v>
+        <v>0.6997</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3509</v>
+        <v>0.5131</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2281</v>
+        <v>0.1866</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.695</v>
+        <v>1.8695</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7602</v>
+        <v>2.2599</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4552</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0338</v>
+        <v>-1.9421</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0987</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9351</v>
+        <v>-2.7249</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.566</v>
+        <v>-2.1062</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2527</v>
+        <v>-1.4384</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3133</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1872</v>
+        <v>0.0814</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5713</v>
+        <v>-0.2246</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3841</v>
+        <v>0.306</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3788</v>
+        <v>-2.1876</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6814</v>
+        <v>-1.2138</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.6974</v>
+        <v>-0.9738</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3152</v>
+        <v>-0.5336</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2211</v>
+        <v>-0.0589</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0941</v>
+        <v>-0.4747</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8695</v>
+        <v>-1.695</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2599</v>
+        <v>0.7602</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3904</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4857</v>
+        <v>-3.7514</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2936</v>
+        <v>-1.4977</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.192</v>
+        <v>-2.2537</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0869</v>
@@ -1234,13 +1234,13 @@
         <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>0.579</v>
+        <v>-0.6868</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2197</v>
+        <v>0.0156</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6408</v>
+        <v>-0.7024</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5275</v>
+        <v>-4.7152</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9031</v>
+        <v>-2.2758</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6244</v>
+        <v>-2.4394</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6524</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2008</v>
+        <v>-1.3886</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.5371</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0364</v>
+        <v>-0.8514</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6743</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.418800000000001</v>
+        <v>-1.7335</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4618</v>
+        <v>10.1468</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.8803</v>
+        <v>-11.8802</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.135500000000001</v>
+        <v>-7.135500000000002</v>
       </c>
       <c r="H12" t="n">
         <v>-0.6530999999999993</v>
@@ -1369,7 +1369,7 @@
         <v>5.918200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.203800000000001</v>
+        <v>7.203799999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-20.2575</v>
@@ -1390,13 +1390,13 @@
         <v>19.5757</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.115</v>
+        <v>-1.4302</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7210999999999999</v>
+        <v>1.4061</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8361</v>
+        <v>-2.836</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7810000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1256</v>
+        <v>9.505800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>8.2562</v>
+        <v>8.703200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8694</v>
+        <v>0.8026</v>
       </c>
       <c r="G13" t="n">
         <v>4.3986</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4455</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4675</v>
+        <v>-0.0204</v>
       </c>
       <c r="U13" t="n">
-        <v>0.022</v>
+        <v>-0.0448</v>
       </c>
       <c r="V13" t="n">
         <v>4.5199</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.763</v>
+        <v>6.0751</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9562</v>
+        <v>4.5923</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1932</v>
+        <v>1.4828</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2778</v>
+        <v>7.0599</v>
       </c>
       <c r="H14" t="n">
-        <v>3.595</v>
+        <v>1.5145</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6829</v>
+        <v>5.5454</v>
       </c>
       <c r="J14" t="n">
-        <v>4.937</v>
+        <v>6.3891</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5983</v>
+        <v>1.3354</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3387</v>
+        <v>5.0538</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6592</v>
+        <v>0.6708</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0033</v>
+        <v>0.1792</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6558</v>
+        <v>0.4916</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7902</v>
+        <v>0.125</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1088</v>
+        <v>0.1406</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6813</v>
+        <v>-0.0156</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0854</v>
+        <v>1.3252</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9087</v>
+        <v>5.8901</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6983</v>
+        <v>6.3915</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2105</v>
+        <v>-0.5014</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0599</v>
+        <v>4.2778</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5145</v>
+        <v>3.595</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5454</v>
+        <v>0.6829</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3891</v>
+        <v>4.937</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3354</v>
+        <v>3.5983</v>
       </c>
       <c r="L15" t="n">
-        <v>5.0538</v>
+        <v>1.3387</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6708</v>
+        <v>-0.6592</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1792</v>
+        <v>-0.0033</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4916</v>
+        <v>-0.6558</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0414</v>
+        <v>1.9173</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7534999999999999</v>
+        <v>1.5442</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2879</v>
+        <v>0.3731</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3252</v>
+        <v>2.0854</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1217</v>
+        <v>0.5038</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3152</v>
+        <v>3.4269</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4369</v>
+        <v>-2.9231</v>
       </c>
       <c r="G16" t="n">
         <v>2.7104</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1372</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6044</v>
+        <v>-0.4927</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5327</v>
+        <v>-0.0189</v>
       </c>
       <c r="V16" t="n">
         <v>-1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8106</v>
+        <v>-1.3013</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3513</v>
+        <v>0.6808</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1619</v>
+        <v>-1.9821</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6688</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7282</v>
+        <v>1.2374</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5502</v>
+        <v>0.8797</v>
       </c>
       <c r="U17" t="n">
-        <v>0.178</v>
+        <v>0.3578</v>
       </c>
       <c r="V17" t="n">
         <v>0.5649999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9385</v>
+        <v>-1.4946</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7756999999999999</v>
+        <v>0.6622</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1628</v>
+        <v>-2.1567</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3949</v>
+        <v>-1.5251</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3382</v>
+        <v>-0.3194</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7332</v>
+        <v>-1.2057</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6874</v>
+        <v>1.7701</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5726</v>
+        <v>1.0434</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1147</v>
+        <v>0.7267</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0823</v>
+        <v>-3.2952</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2344</v>
+        <v>-1.3628</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8479</v>
+        <v>-1.9324</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.0451</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3716</v>
+        <v>-0.0565</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.0204</v>
       </c>
       <c r="U18" t="n">
-        <v>0.702</v>
+        <v>-0.0361</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3372</v>
+        <v>-1.8126</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2151</v>
+        <v>-0.5522</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5523</v>
+        <v>-1.2603</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5251</v>
+        <v>-0.3949</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3194</v>
+        <v>1.3382</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2057</v>
+        <v>-1.7332</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7701</v>
+        <v>1.6874</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0434</v>
+        <v>1.5726</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7267</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2952</v>
+        <v>-2.0823</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3628</v>
+        <v>-0.2344</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9324</v>
+        <v>-1.8479</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8991</v>
+        <v>0.4975</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>-0.1069</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4317</v>
+        <v>0.6044</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.7395</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4554</v>
+        <v>-2.7294</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9346</v>
+        <v>-3.0029</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4793</v>
+        <v>0.2735</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1816</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5664</v>
+        <v>0.0243</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3849</v>
+        <v>0.7514</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4244</v>
+        <v>0.9528</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3806</v>
+        <v>0.6086</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9562</v>
+        <v>0.3442</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7572</v>
+        <v>-0.1771</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1858</v>
+        <v>-0.5843</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5714</v>
+        <v>0.4072</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2705</v>
+        <v>0.3866</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2091</v>
+        <v>0.7859</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0614</v>
+        <v>-0.3993</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1093</v>
+        <v>-2.8042</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.5443</v>
+        <v>-1.479</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4738</v>
+        <v>-2.8073</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4441</v>
+        <v>-3.1582</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0296</v>
+        <v>0.3509</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7756999999999999</v>
+        <v>-1.1816</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0243</v>
+        <v>-1.5664</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7514</v>
+        <v>0.3849</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9528</v>
+        <v>-0.4244</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6086</v>
+        <v>-1.3806</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3442</v>
+        <v>0.9562</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1771</v>
+        <v>-0.7572</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5843</v>
+        <v>-0.1858</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4072</v>
+        <v>-0.5714</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6423</v>
+        <v>-0.0814</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3447</v>
+        <v>-0.0144</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7024</v>
+        <v>-0.067</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8042</v>
+        <v>-1.1093</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.479</v>
+        <v>-0.5443</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.241400000000001</v>
+        <v>-7.9209</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7574</v>
+        <v>-5.8633</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.484</v>
+        <v>-2.0576</v>
       </c>
       <c r="G22" t="n">
         <v>-6.3166</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1646</v>
+        <v>0.1559</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.1406</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4111</v>
+        <v>0.0153</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.418699999999998</v>
+        <v>3.908700000000003</v>
       </c>
       <c r="E23" t="n">
-        <v>11.8805</v>
+        <v>11.8803</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.461500000000001</v>
+        <v>-7.971399999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>7.135400000000002</v>
+        <v>7.1354</v>
       </c>
       <c r="H23" t="n">
         <v>0.653</v>
       </c>
       <c r="I23" t="n">
-        <v>6.482400000000002</v>
+        <v>6.4824</v>
       </c>
       <c r="J23" t="n">
         <v>20.2575</v>
       </c>
       <c r="K23" t="n">
-        <v>6.5714</v>
+        <v>6.571399999999999</v>
       </c>
       <c r="L23" t="n">
         <v>13.6861</v>
@@ -2233,7 +2233,7 @@
         <v>-13.122</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.918099999999999</v>
+        <v>-5.9181</v>
       </c>
       <c r="O23" t="n">
         <v>-7.2037</v>
@@ -2248,19 +2248,19 @@
         <v>11.9629</v>
       </c>
       <c r="S23" t="n">
-        <v>2.115</v>
+        <v>3.605</v>
       </c>
       <c r="T23" t="n">
-        <v>2.835900000000001</v>
+        <v>2.8362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7211000000000001</v>
+        <v>0.7689</v>
       </c>
       <c r="V23" t="n">
         <v>0.7808999999999997</v>
       </c>
       <c r="W23" t="n">
-        <v>8.362399999999997</v>
+        <v>8.362399999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-7.581499999999999</v>
